--- a/i_test/test_D3_coorte_con_caratterizzazione/ese_gastro.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/ese_gastro.xlsx
@@ -167,7 +167,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>20230101</v>
+        <v>20230102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
